--- a/research/traditional_assets/database/data/oman/oman_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0009700000000000001</v>
+        <v>0.0242</v>
       </c>
       <c r="E2">
-        <v>-0.0403</v>
+        <v>-0.00544</v>
+      </c>
+      <c r="F2">
+        <v>0.05</v>
       </c>
       <c r="G2">
-        <v>0.1199245757385292</v>
+        <v>0.08515592515592516</v>
       </c>
       <c r="H2">
-        <v>0.1199245757385292</v>
+        <v>0.08515592515592516</v>
       </c>
       <c r="I2">
-        <v>0.1145820238843494</v>
+        <v>0.05014553014553016</v>
       </c>
       <c r="J2">
-        <v>0.101141685180756</v>
+        <v>0.04482806694810666</v>
       </c>
       <c r="K2">
-        <v>17.5</v>
+        <v>8.440000000000001</v>
       </c>
       <c r="L2">
-        <v>0.1099937146448774</v>
+        <v>0.0350935550935551</v>
       </c>
       <c r="M2">
-        <v>14.97</v>
+        <v>18.22</v>
       </c>
       <c r="N2">
-        <v>0.06898617511520737</v>
+        <v>0.07560165975103735</v>
       </c>
       <c r="O2">
-        <v>0.8554285714285713</v>
+        <v>2.158767772511848</v>
       </c>
       <c r="P2">
-        <v>14.97</v>
+        <v>18.22</v>
       </c>
       <c r="Q2">
-        <v>0.06898617511520737</v>
+        <v>0.07560165975103735</v>
       </c>
       <c r="R2">
-        <v>0.8554285714285713</v>
+        <v>2.158767772511848</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>25.525</v>
+        <v>74.22</v>
       </c>
       <c r="V2">
-        <v>0.1176267281105991</v>
+        <v>0.3079668049792531</v>
       </c>
       <c r="W2">
-        <v>0.07022993400042579</v>
+        <v>0.09676966292134831</v>
       </c>
       <c r="X2">
-        <v>0.07040722999877942</v>
+        <v>0.1134759674624535</v>
       </c>
       <c r="Y2">
-        <v>-0.0001772959983536299</v>
+        <v>-0.01670630454110522</v>
       </c>
       <c r="Z2">
-        <v>0.7175264055129119</v>
+        <v>0.7413663952947124</v>
       </c>
       <c r="AA2">
-        <v>0.07539591399910681</v>
+        <v>0.09411133841911468</v>
       </c>
       <c r="AB2">
-        <v>0.0698631646347974</v>
+        <v>0.1131972746001007</v>
       </c>
       <c r="AC2">
-        <v>0.005585430617493517</v>
+        <v>-0.02027420715351259</v>
       </c>
       <c r="AD2">
-        <v>8.720000000000001</v>
+        <v>15.448</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.720000000000001</v>
+        <v>15.448</v>
       </c>
       <c r="AG2">
-        <v>-16.805</v>
+        <v>-58.772</v>
       </c>
       <c r="AH2">
-        <v>0.03863193336877548</v>
+        <v>0.06023833291739457</v>
       </c>
       <c r="AI2">
-        <v>0.03143248504073246</v>
+        <v>0.04188175074827572</v>
       </c>
       <c r="AJ2">
-        <v>-0.08394315542346213</v>
+        <v>-0.3225190420791536</v>
       </c>
       <c r="AK2">
-        <v>-0.0667143055638262</v>
+        <v>-0.1994786646211494</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="AN2">
-        <v>0.4410723318158827</v>
+        <v>1.089421720733427</v>
+      </c>
+      <c r="AO2">
+        <v>18.63987635239567</v>
       </c>
       <c r="AP2">
-        <v>-0.8500252908447142</v>
+        <v>-4.144710860366714</v>
+      </c>
+      <c r="AQ2">
+        <v>18.63987635239567</v>
       </c>
     </row>
     <row r="3">
@@ -715,41 +724,47 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0515</v>
+      </c>
+      <c r="E3">
+        <v>0.08689999999999999</v>
+      </c>
       <c r="G3">
-        <v>0.2290322580645161</v>
+        <v>0.2622418879056048</v>
       </c>
       <c r="H3">
-        <v>0.2290322580645161</v>
+        <v>0.2622418879056048</v>
       </c>
       <c r="I3">
-        <v>0.3835125448028674</v>
+        <v>0.2790560471976402</v>
       </c>
       <c r="J3">
-        <v>0.3626523297491039</v>
+        <v>0.256375321659449</v>
       </c>
       <c r="K3">
-        <v>10.1</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L3">
-        <v>0.3620071684587814</v>
+        <v>0.2548672566371682</v>
       </c>
       <c r="M3">
-        <v>1.3</v>
+        <v>1.82</v>
       </c>
       <c r="N3">
-        <v>0.02338129496402878</v>
+        <v>0.03493282149712092</v>
       </c>
       <c r="O3">
-        <v>0.1287128712871287</v>
+        <v>0.2106481481481481</v>
       </c>
       <c r="P3">
-        <v>1.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>0.02338129496402878</v>
+        <v>0.03493282149712092</v>
       </c>
       <c r="R3">
-        <v>0.1287128712871287</v>
+        <v>0.2106481481481481</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +773,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.47</v>
+        <v>19.1</v>
       </c>
       <c r="V3">
-        <v>0.06241007194244604</v>
+        <v>0.3666026871401152</v>
       </c>
       <c r="W3">
-        <v>0.2387706855791962</v>
+        <v>0.162406015037594</v>
       </c>
       <c r="X3">
-        <v>0.069589605417102</v>
+        <v>0.1134759674624535</v>
       </c>
       <c r="Y3">
-        <v>0.1691810801620942</v>
+        <v>0.04893004757514047</v>
       </c>
       <c r="Z3">
-        <v>0.7517784005173529</v>
+        <v>0.71269394105033</v>
       </c>
       <c r="AA3">
-        <v>0.2726341884026731</v>
+        <v>0.1827171383815187</v>
       </c>
       <c r="AB3">
-        <v>0.06947923902579407</v>
+        <v>0.1131972746001007</v>
       </c>
       <c r="AC3">
-        <v>0.203154949376879</v>
+        <v>0.06951986378141806</v>
       </c>
       <c r="AD3">
-        <v>0.26</v>
+        <v>0.408</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.26</v>
+        <v>0.408</v>
       </c>
       <c r="AG3">
-        <v>-3.21</v>
+        <v>-18.692</v>
       </c>
       <c r="AH3">
-        <v>0.004654493376297888</v>
+        <v>0.007770244534166222</v>
       </c>
       <c r="AI3">
-        <v>0.005072181037846274</v>
+        <v>0.006844718829687289</v>
       </c>
       <c r="AJ3">
-        <v>-0.06127123496850544</v>
+        <v>-0.5595067049808429</v>
       </c>
       <c r="AK3">
-        <v>-0.06716886377903328</v>
+        <v>-0.461439715611731</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.02385321100917431</v>
+        <v>0.04210526315789474</v>
       </c>
       <c r="AP3">
-        <v>-0.2944954128440367</v>
+        <v>-1.928998968008256</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oman United Insurance Company SAOG (MSM:OUIC)</t>
+          <t>Dhofar Insurance Company SAOG (MSM:DICS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,46 +853,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0479</v>
-      </c>
-      <c r="E4">
-        <v>-0.061</v>
+        <v>0.0242</v>
       </c>
       <c r="G4">
-        <v>0.2621184919210054</v>
+        <v>0.1182033096926714</v>
       </c>
       <c r="H4">
-        <v>0.2621184919210054</v>
+        <v>0.1182033096926714</v>
       </c>
       <c r="I4">
-        <v>0.1831238779174147</v>
+        <v>0.1108747044917258</v>
       </c>
       <c r="J4">
-        <v>0.1511669658886894</v>
+        <v>0.1028463611516789</v>
       </c>
       <c r="K4">
-        <v>8.44</v>
+        <v>6.89</v>
       </c>
       <c r="L4">
-        <v>0.1515260323159784</v>
+        <v>0.0814420803782506</v>
       </c>
       <c r="M4">
-        <v>9.109999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="N4">
-        <v>0.0932446264073695</v>
+        <v>0.06842105263157895</v>
       </c>
       <c r="O4">
-        <v>1.079383886255924</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="P4">
-        <v>9.109999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="Q4">
-        <v>0.0932446264073695</v>
+        <v>0.06842105263157895</v>
       </c>
       <c r="R4">
-        <v>1.079383886255924</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,67 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.489</v>
+        <v>20.1</v>
       </c>
       <c r="V4">
-        <v>0.005005117707267144</v>
+        <v>0.3526315789473685</v>
       </c>
       <c r="W4">
-        <v>0.1096103896103896</v>
+        <v>0.09676966292134831</v>
       </c>
       <c r="X4">
-        <v>0.07122485458045684</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="Y4">
-        <v>0.03838553502993276</v>
+        <v>-0.01621251606371522</v>
       </c>
       <c r="Z4">
-        <v>0.7197870360798098</v>
+        <v>1.163206379760759</v>
       </c>
       <c r="AA4">
-        <v>0.1088080223301974</v>
+        <v>0.1196315434268119</v>
       </c>
       <c r="AB4">
-        <v>0.07024709024380073</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="AC4">
-        <v>0.0385609320863967</v>
+        <v>0.006649364441748407</v>
       </c>
       <c r="AD4">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>3.431</v>
+        <v>-20.1</v>
       </c>
       <c r="AH4">
-        <v>0.03857508364495178</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.04880478087649402</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.03392629361916722</v>
+        <v>-0.5447154471544716</v>
       </c>
       <c r="AK4">
-        <v>0.04297829164109181</v>
+        <v>-0.384321223709369</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="AN4">
-        <v>0.3531531531531532</v>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>14.49768160741886</v>
       </c>
       <c r="AP4">
-        <v>0.3090990990990991</v>
+        <v>-2.012012012012012</v>
+      </c>
+      <c r="AQ4">
+        <v>14.49768160741886</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Madina Insurance Company SAOG (MSM:AMAT)</t>
+          <t>Oman United Insurance Company SAOG (MSM:OUIC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,46 +984,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0009700000000000001</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.0196</v>
+        <v>-0.00544</v>
+      </c>
+      <c r="F5">
+        <v>0.05</v>
       </c>
       <c r="G5">
-        <v>0.07119047619047619</v>
+        <v>0.2471264367816092</v>
       </c>
       <c r="H5">
-        <v>0.07119047619047619</v>
+        <v>0.2471264367816092</v>
       </c>
       <c r="I5">
-        <v>0.065</v>
+        <v>0.1693486590038314</v>
       </c>
       <c r="J5">
-        <v>0.04938095238095238</v>
+        <v>0.1439272463091253</v>
       </c>
       <c r="K5">
-        <v>2.07</v>
+        <v>7.53</v>
       </c>
       <c r="L5">
-        <v>0.04928571428571428</v>
+        <v>0.1442528735632184</v>
       </c>
       <c r="M5">
-        <v>4.56</v>
+        <v>9.09</v>
       </c>
       <c r="N5">
-        <v>0.1055555555555555</v>
+        <v>0.1163892445582587</v>
       </c>
       <c r="O5">
-        <v>2.202898550724638</v>
+        <v>1.207171314741036</v>
       </c>
       <c r="P5">
-        <v>4.56</v>
+        <v>9.09</v>
       </c>
       <c r="Q5">
-        <v>0.1055555555555555</v>
+        <v>0.1163892445582587</v>
       </c>
       <c r="R5">
-        <v>2.202898550724638</v>
+        <v>1.207171314741036</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1014,55 +1035,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>21.4</v>
+        <v>9.01</v>
       </c>
       <c r="V5">
-        <v>0.4953703703703703</v>
+        <v>0.1153649167733675</v>
       </c>
       <c r="W5">
-        <v>0.030849478390462</v>
+        <v>0.09856020942408376</v>
       </c>
       <c r="X5">
-        <v>0.06937387651942586</v>
+        <v>0.1154365547916884</v>
       </c>
       <c r="Y5">
-        <v>-0.03852439812896387</v>
+        <v>-0.01687634536760466</v>
       </c>
       <c r="Z5">
-        <v>0.8502024291497977</v>
+        <v>0.6538813242975786</v>
       </c>
       <c r="AA5">
-        <v>0.0419838056680162</v>
+        <v>0.09411133841911468</v>
       </c>
       <c r="AB5">
-        <v>0.06937387651942586</v>
+        <v>0.1143855455726273</v>
       </c>
       <c r="AC5">
-        <v>-0.02739007085140967</v>
+        <v>-0.02027420715351259</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AG5">
-        <v>-21.4</v>
+        <v>-5.97</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.03746610796154794</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.03910470800102907</v>
       </c>
       <c r="AJ5">
-        <v>-0.9816513761467888</v>
+        <v>-0.08276722584222931</v>
       </c>
       <c r="AK5">
-        <v>-0.5059101654846335</v>
+        <v>-0.08686163247490178</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1071,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.3169968717413973</v>
       </c>
       <c r="AP5">
-        <v>-7.039473684210526</v>
+        <v>-0.6225234619395204</v>
       </c>
     </row>
     <row r="6">
@@ -1085,118 +1106,246 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Al Madina Insurance Company SAOG (MSM:AMAT)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0298</v>
+      </c>
+      <c r="E6">
+        <v>-0.205</v>
+      </c>
+      <c r="G6">
+        <v>0.09346590909090909</v>
+      </c>
+      <c r="H6">
+        <v>0.09346590909090909</v>
+      </c>
+      <c r="I6">
+        <v>0.05056818181818182</v>
+      </c>
+      <c r="J6">
+        <v>0.03911931818181818</v>
+      </c>
+      <c r="K6">
+        <v>1.38</v>
+      </c>
+      <c r="L6">
+        <v>0.03920454545454545</v>
+      </c>
+      <c r="M6">
+        <v>3.41</v>
+      </c>
+      <c r="N6">
+        <v>0.08317073170731708</v>
+      </c>
+      <c r="O6">
+        <v>2.471014492753624</v>
+      </c>
+      <c r="P6">
+        <v>3.41</v>
+      </c>
+      <c r="Q6">
+        <v>0.08317073170731708</v>
+      </c>
+      <c r="R6">
+        <v>2.471014492753624</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>18</v>
+      </c>
+      <c r="V6">
+        <v>0.4390243902439024</v>
+      </c>
+      <c r="W6">
+        <v>0.0216640502354788</v>
+      </c>
+      <c r="X6">
+        <v>0.1129821789850635</v>
+      </c>
+      <c r="Y6">
+        <v>-0.09131812874958473</v>
+      </c>
+      <c r="Z6">
+        <v>0.8321513002364066</v>
+      </c>
+      <c r="AA6">
+        <v>0.0325531914893617</v>
+      </c>
+      <c r="AB6">
+        <v>0.1129821789850635</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08042898749570183</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-18</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.7826086956521739</v>
+      </c>
+      <c r="AK6">
+        <v>-0.4556962025316456</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>-8.530805687203792</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Takaful Oman Insurance SAOG (MSM:TAOI)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.104</v>
-      </c>
-      <c r="G6">
-        <v>-0.1462686567164179</v>
-      </c>
-      <c r="H6">
-        <v>-0.1462686567164179</v>
-      </c>
-      <c r="I6">
-        <v>-0.1611940298507463</v>
-      </c>
-      <c r="J6">
-        <v>-0.1611940298507463</v>
-      </c>
-      <c r="K6">
-        <v>-3.11</v>
-      </c>
-      <c r="L6">
-        <v>-0.09283582089552238</v>
-      </c>
-      <c r="M6">
+      <c r="D7">
+        <v>0.07919999999999999</v>
+      </c>
+      <c r="G7">
+        <v>-0.4219653179190751</v>
+      </c>
+      <c r="H7">
+        <v>-0.4219653179190751</v>
+      </c>
+      <c r="I7">
+        <v>-0.5028901734104045</v>
+      </c>
+      <c r="J7">
+        <v>-0.5028901734104045</v>
+      </c>
+      <c r="K7">
+        <v>-16</v>
+      </c>
+      <c r="L7">
+        <v>-0.4624277456647399</v>
+      </c>
+      <c r="M7">
         <v>-0</v>
       </c>
-      <c r="N6">
+      <c r="N7">
         <v>-0</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>-0</v>
       </c>
-      <c r="Q6">
+      <c r="Q7">
         <v>-0</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0.166</v>
-      </c>
-      <c r="V6">
-        <v>0.008097560975609756</v>
-      </c>
-      <c r="W6">
-        <v>-0.05437062937062936</v>
-      </c>
-      <c r="X6">
-        <v>0.07959060283593632</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1339612322065657</v>
-      </c>
-      <c r="Z6">
-        <v>0.5792039835402331</v>
-      </c>
-      <c r="AA6">
-        <v>-0.09336422421245548</v>
-      </c>
-      <c r="AB6">
-        <v>0.07465934901551247</v>
-      </c>
-      <c r="AC6">
-        <v>-0.168023573227968</v>
-      </c>
-      <c r="AD6">
-        <v>4.54</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>4.54</v>
-      </c>
-      <c r="AG6">
-        <v>4.374</v>
-      </c>
-      <c r="AH6">
-        <v>0.1813099041533546</v>
-      </c>
-      <c r="AI6">
-        <v>0.05527148770392014</v>
-      </c>
-      <c r="AJ6">
-        <v>0.1758462651764895</v>
-      </c>
-      <c r="AK6">
-        <v>0.05335838192597653</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>-0.8614800759013284</v>
-      </c>
-      <c r="AP6">
-        <v>-0.8299810246679317</v>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>8.01</v>
+      </c>
+      <c r="V7">
+        <v>0.62578125</v>
+      </c>
+      <c r="W7">
+        <v>-0.2061855670103093</v>
+      </c>
+      <c r="X7">
+        <v>0.172096102863786</v>
+      </c>
+      <c r="Y7">
+        <v>-0.3782816698740953</v>
+      </c>
+      <c r="Z7">
+        <v>0.4220850513577476</v>
+      </c>
+      <c r="AA7">
+        <v>-0.2122624246712372</v>
+      </c>
+      <c r="AB7">
+        <v>0.1263766767962246</v>
+      </c>
+      <c r="AC7">
+        <v>-0.3386391014674618</v>
+      </c>
+      <c r="AD7">
+        <v>12</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>12</v>
+      </c>
+      <c r="AG7">
+        <v>3.99</v>
+      </c>
+      <c r="AH7">
+        <v>0.4838709677419354</v>
+      </c>
+      <c r="AI7">
+        <v>0.1181102362204725</v>
+      </c>
+      <c r="AJ7">
+        <v>0.2376414532459798</v>
+      </c>
+      <c r="AK7">
+        <v>0.04263275991024683</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>-0.6976744186046512</v>
+      </c>
+      <c r="AP7">
+        <v>-0.2319767441860465</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/oman/oman_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0242</v>
+        <v>0.03071</v>
       </c>
       <c r="E2">
-        <v>-0.00544</v>
-      </c>
-      <c r="F2">
-        <v>0.05</v>
+        <v>0.221</v>
       </c>
       <c r="G2">
-        <v>0.08515592515592516</v>
+        <v>0.08242904841402338</v>
       </c>
       <c r="H2">
-        <v>0.08515592515592516</v>
+        <v>0.08242904841402338</v>
       </c>
       <c r="I2">
-        <v>0.05014553014553016</v>
+        <v>0.08877295492487479</v>
       </c>
       <c r="J2">
-        <v>0.04482806694810666</v>
+        <v>0.08068488682563071</v>
       </c>
       <c r="K2">
-        <v>8.440000000000001</v>
+        <v>58.86</v>
       </c>
       <c r="L2">
-        <v>0.0350935550935551</v>
+        <v>0.2456594323873122</v>
       </c>
       <c r="M2">
-        <v>18.22</v>
+        <v>13.17</v>
       </c>
       <c r="N2">
-        <v>0.07560165975103735</v>
+        <v>0.0626844359828653</v>
       </c>
       <c r="O2">
-        <v>2.158767772511848</v>
+        <v>0.2237512742099898</v>
       </c>
       <c r="P2">
-        <v>18.22</v>
+        <v>13.17</v>
       </c>
       <c r="Q2">
-        <v>0.07560165975103735</v>
+        <v>0.0626844359828653</v>
       </c>
       <c r="R2">
-        <v>2.158767772511848</v>
+        <v>0.2237512742099898</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>74.22</v>
+        <v>35.274</v>
       </c>
       <c r="V2">
-        <v>0.3079668049792531</v>
+        <v>0.1678914802475012</v>
       </c>
       <c r="W2">
-        <v>0.09676966292134831</v>
+        <v>0.1350298061490899</v>
       </c>
       <c r="X2">
-        <v>0.1134759674624535</v>
+        <v>0.09207496247073282</v>
       </c>
       <c r="Y2">
-        <v>-0.01670630454110522</v>
+        <v>0.04295484367835706</v>
       </c>
       <c r="Z2">
-        <v>0.7413663952947124</v>
+        <v>0.9527596627962461</v>
       </c>
       <c r="AA2">
-        <v>0.09411133841911468</v>
+        <v>0.08793758184199041</v>
       </c>
       <c r="AB2">
-        <v>0.1131972746001007</v>
+        <v>0.09085882732998929</v>
       </c>
       <c r="AC2">
-        <v>-0.02027420715351259</v>
+        <v>-0.002409183659626384</v>
       </c>
       <c r="AD2">
-        <v>15.448</v>
+        <v>23.372</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.448</v>
+        <v>23.372</v>
       </c>
       <c r="AG2">
-        <v>-58.772</v>
+        <v>-11.902</v>
       </c>
       <c r="AH2">
-        <v>0.06023833291739457</v>
+        <v>0.1001062225877193</v>
       </c>
       <c r="AI2">
-        <v>0.04188175074827572</v>
+        <v>0.0817854793331747</v>
       </c>
       <c r="AJ2">
-        <v>-0.3225190420791536</v>
+        <v>-0.06005106005106006</v>
       </c>
       <c r="AK2">
-        <v>-0.1994786646211494</v>
+        <v>-0.04751335340002715</v>
       </c>
       <c r="AL2">
-        <v>0.647</v>
+        <v>0.701</v>
       </c>
       <c r="AM2">
-        <v>0.647</v>
+        <v>0.701</v>
       </c>
       <c r="AN2">
-        <v>1.089421720733427</v>
+        <v>1.023292469352014</v>
       </c>
       <c r="AO2">
-        <v>18.63987635239567</v>
+        <v>30.34236804564907</v>
       </c>
       <c r="AP2">
-        <v>-4.144710860366714</v>
+        <v>-0.5211033274956217</v>
       </c>
       <c r="AQ2">
-        <v>18.63987635239567</v>
+        <v>30.34236804564907</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oman Qatar Insurance Company SAOG (MSM:OQIC)</t>
+          <t>Dhofar Insurance Company SAOG (MSM:DICS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0515</v>
+        <v>0.0574</v>
       </c>
       <c r="E3">
-        <v>0.08689999999999999</v>
+        <v>0.274</v>
       </c>
       <c r="G3">
-        <v>0.2622418879056048</v>
+        <v>0.1339977851605759</v>
       </c>
       <c r="H3">
-        <v>0.2622418879056048</v>
+        <v>0.1339977851605759</v>
       </c>
       <c r="I3">
-        <v>0.2790560471976402</v>
+        <v>0.1672203765227021</v>
       </c>
       <c r="J3">
-        <v>0.256375321659449</v>
+        <v>0.1474790820721053</v>
       </c>
       <c r="K3">
-        <v>8.640000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="L3">
-        <v>0.2548672566371682</v>
+        <v>0.1406423034330011</v>
       </c>
       <c r="M3">
-        <v>1.82</v>
+        <v>4.08</v>
       </c>
       <c r="N3">
-        <v>0.03493282149712092</v>
+        <v>0.05779036827195468</v>
       </c>
       <c r="O3">
-        <v>0.2106481481481481</v>
+        <v>0.3212598425196851</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>4.08</v>
       </c>
       <c r="Q3">
-        <v>0.03493282149712092</v>
+        <v>0.05779036827195468</v>
       </c>
       <c r="R3">
-        <v>0.2106481481481481</v>
+        <v>0.3212598425196851</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.1</v>
+        <v>26.4</v>
       </c>
       <c r="V3">
-        <v>0.3666026871401152</v>
+        <v>0.3739376770538244</v>
       </c>
       <c r="W3">
-        <v>0.162406015037594</v>
+        <v>0.1754143646408839</v>
       </c>
       <c r="X3">
-        <v>0.1134759674624535</v>
+        <v>0.0934378060977071</v>
       </c>
       <c r="Y3">
-        <v>0.04893004757514047</v>
+        <v>0.08197655854317684</v>
       </c>
       <c r="Z3">
-        <v>0.71269394105033</v>
+        <v>1.726577437858508</v>
       </c>
       <c r="AA3">
-        <v>0.1827171383815187</v>
+        <v>0.2546340556617803</v>
       </c>
       <c r="AB3">
-        <v>0.1131972746001007</v>
+        <v>0.09124862670625236</v>
       </c>
       <c r="AC3">
-        <v>0.06951986378141806</v>
+        <v>0.1633854289555279</v>
       </c>
       <c r="AD3">
-        <v>0.408</v>
+        <v>5.19</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.408</v>
+        <v>5.19</v>
       </c>
       <c r="AG3">
-        <v>-18.692</v>
+        <v>-21.21</v>
       </c>
       <c r="AH3">
-        <v>0.007770244534166222</v>
+        <v>0.06847869112020057</v>
       </c>
       <c r="AI3">
-        <v>0.006844718829687289</v>
+        <v>0.05617491070462172</v>
       </c>
       <c r="AJ3">
-        <v>-0.5595067049808429</v>
+        <v>-0.4294391577242356</v>
       </c>
       <c r="AK3">
-        <v>-0.461439715611731</v>
+        <v>-0.3214123352023033</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.701</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.701</v>
       </c>
       <c r="AN3">
-        <v>0.04210526315789474</v>
+        <v>0.3348387096774194</v>
+      </c>
+      <c r="AO3">
+        <v>21.54065620542083</v>
       </c>
       <c r="AP3">
-        <v>-1.928998968008256</v>
+        <v>-1.368387096774193</v>
+      </c>
+      <c r="AQ3">
+        <v>21.54065620542083</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dhofar Insurance Company SAOG (MSM:DICS)</t>
+          <t>Oman United Insurance Company SAOG (MSM:OUIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,43 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0242</v>
+        <v>-0.0141</v>
+      </c>
+      <c r="E4">
+        <v>-0.031</v>
       </c>
       <c r="G4">
-        <v>0.1182033096926714</v>
+        <v>0.1492359932088285</v>
       </c>
       <c r="H4">
-        <v>0.1182033096926714</v>
+        <v>0.1492359932088285</v>
       </c>
       <c r="I4">
-        <v>0.1108747044917258</v>
+        <v>0.1278438030560272</v>
       </c>
       <c r="J4">
-        <v>0.1028463611516789</v>
+        <v>0.12</v>
       </c>
       <c r="K4">
-        <v>6.89</v>
+        <v>7.07</v>
       </c>
       <c r="L4">
-        <v>0.0814420803782506</v>
+        <v>0.1200339558573854</v>
       </c>
       <c r="M4">
-        <v>3.9</v>
+        <v>9.09</v>
       </c>
       <c r="N4">
-        <v>0.06842105263157895</v>
+        <v>0.1296718972895863</v>
       </c>
       <c r="O4">
-        <v>0.5660377358490566</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="P4">
-        <v>3.9</v>
+        <v>9.09</v>
       </c>
       <c r="Q4">
-        <v>0.06842105263157895</v>
+        <v>0.1296718972895863</v>
       </c>
       <c r="R4">
-        <v>0.5660377358490566</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +904,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>20.1</v>
+        <v>0.634</v>
       </c>
       <c r="V4">
-        <v>0.3526315789473685</v>
+        <v>0.009044222539229672</v>
       </c>
       <c r="W4">
-        <v>0.09676966292134831</v>
+        <v>0.09464524765729584</v>
       </c>
       <c r="X4">
-        <v>0.1129821789850635</v>
+        <v>0.09071211884375854</v>
       </c>
       <c r="Y4">
-        <v>-0.01621251606371522</v>
+        <v>0.003933128813537301</v>
       </c>
       <c r="Z4">
-        <v>1.163206379760759</v>
+        <v>0.8569765750036373</v>
       </c>
       <c r="AA4">
-        <v>0.1196315434268119</v>
+        <v>0.1028371890004365</v>
       </c>
       <c r="AB4">
-        <v>0.1129821789850635</v>
+        <v>0.09046902795372622</v>
       </c>
       <c r="AC4">
-        <v>0.006649364441748407</v>
+        <v>0.01236816104671028</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="AG4">
-        <v>-20.1</v>
+        <v>0.148</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.01103242007844023</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.01067110613793292</v>
       </c>
       <c r="AJ4">
-        <v>-0.5447154471544716</v>
+        <v>0.002106821546520898</v>
       </c>
       <c r="AK4">
-        <v>-0.384321223709369</v>
+        <v>0.00203722057042176</v>
       </c>
       <c r="AL4">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>14.49768160741886</v>
+        <v>0.09433051869722558</v>
       </c>
       <c r="AP4">
-        <v>-2.012012012012012</v>
-      </c>
-      <c r="AQ4">
-        <v>14.49768160741886</v>
+        <v>0.01785283474065139</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oman United Insurance Company SAOG (MSM:OUIC)</t>
+          <t>Al Madina Insurance Company SAOG (MSM:AMAT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,106 +984,100 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.05019999999999999</v>
+        <v>0.00402</v>
       </c>
       <c r="E5">
-        <v>-0.00544</v>
-      </c>
-      <c r="F5">
-        <v>0.05</v>
+        <v>0.168</v>
       </c>
       <c r="G5">
-        <v>0.2471264367816092</v>
+        <v>0.08197802197802198</v>
       </c>
       <c r="H5">
-        <v>0.2471264367816092</v>
+        <v>0.08197802197802198</v>
       </c>
       <c r="I5">
-        <v>0.1693486590038314</v>
+        <v>0.0778021978021978</v>
       </c>
       <c r="J5">
-        <v>0.1439272463091253</v>
+        <v>0.06340659340659341</v>
       </c>
       <c r="K5">
-        <v>7.53</v>
+        <v>2.89</v>
       </c>
       <c r="L5">
-        <v>0.1442528735632184</v>
+        <v>0.06351648351648352</v>
       </c>
       <c r="M5">
-        <v>9.09</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1163892445582587</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.207171314741036</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>9.09</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.1163892445582587</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.207171314741036</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>9.01</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.1153649167733675</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.09856020942408376</v>
+        <v>0.05026086956521739</v>
       </c>
       <c r="X5">
-        <v>0.1154365547916884</v>
+        <v>0.09022450304950735</v>
       </c>
       <c r="Y5">
-        <v>-0.01687634536760466</v>
+        <v>-0.03996363348428996</v>
       </c>
       <c r="Z5">
-        <v>0.6538813242975786</v>
+        <v>1.151898734177215</v>
       </c>
       <c r="AA5">
-        <v>0.09411133841911468</v>
+        <v>0.07303797468354431</v>
       </c>
       <c r="AB5">
-        <v>0.1143855455726273</v>
+        <v>0.09022450304950735</v>
       </c>
       <c r="AC5">
-        <v>-0.02027420715351259</v>
+        <v>-0.01718652836596304</v>
       </c>
       <c r="AD5">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-5.97</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.03746610796154794</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.03910470800102907</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.08276722584222931</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>-0.08686163247490178</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1092,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.3169968717413973</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-0.6225234619395204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Madina Insurance Company SAOG (MSM:AMAT)</t>
+          <t>Takaful Oman Insurance SAOG (MSM:TAOI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,103 +1109,100 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0298</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.205</v>
+        <v>0.532</v>
       </c>
       <c r="G6">
-        <v>0.09346590909090909</v>
+        <v>-0.1084632516703786</v>
       </c>
       <c r="H6">
-        <v>0.09346590909090909</v>
+        <v>-0.1084632516703786</v>
       </c>
       <c r="I6">
-        <v>0.05056818181818182</v>
+        <v>-0.1091314031180401</v>
       </c>
       <c r="J6">
-        <v>0.03911931818181818</v>
+        <v>-0.1091314031180401</v>
       </c>
       <c r="K6">
-        <v>1.38</v>
+        <v>36.2</v>
       </c>
       <c r="L6">
-        <v>0.03920454545454545</v>
+        <v>0.8062360801781738</v>
       </c>
       <c r="M6">
-        <v>3.41</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.08317073170731708</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>2.471014492753624</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>3.41</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.08317073170731708</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>2.471014492753624</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>18</v>
+        <v>8.24</v>
       </c>
       <c r="V6">
-        <v>0.4390243902439024</v>
+        <v>0.2641025641025641</v>
       </c>
       <c r="W6">
-        <v>0.0216640502354788</v>
+        <v>0.4788359788359789</v>
       </c>
       <c r="X6">
-        <v>0.1129821789850635</v>
+        <v>0.1146016953604757</v>
       </c>
       <c r="Y6">
-        <v>-0.09131812874958473</v>
+        <v>0.3642342834755031</v>
       </c>
       <c r="Z6">
-        <v>0.8321513002364066</v>
+        <v>0.4936778449697636</v>
       </c>
       <c r="AA6">
-        <v>0.0325531914893617</v>
+        <v>-0.05387575590984058</v>
       </c>
       <c r="AB6">
-        <v>0.1129821789850635</v>
+        <v>0.09815983842831374</v>
       </c>
       <c r="AC6">
-        <v>-0.08042898749570183</v>
+        <v>-0.1520355943381543</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="AG6">
-        <v>-18</v>
+        <v>9.159999999999998</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.3580246913580247</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.2693498452012384</v>
       </c>
       <c r="AJ6">
-        <v>-0.7826086956521739</v>
+        <v>0.2269573835480674</v>
       </c>
       <c r="AK6">
-        <v>-0.4556962025316456</v>
+        <v>0.162526614620298</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1220,132 +1211,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>-3.632567849686847</v>
       </c>
       <c r="AP6">
-        <v>-8.530805687203792</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Takaful Oman Insurance SAOG (MSM:TAOI)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.07919999999999999</v>
-      </c>
-      <c r="G7">
-        <v>-0.4219653179190751</v>
-      </c>
-      <c r="H7">
-        <v>-0.4219653179190751</v>
-      </c>
-      <c r="I7">
-        <v>-0.5028901734104045</v>
-      </c>
-      <c r="J7">
-        <v>-0.5028901734104045</v>
-      </c>
-      <c r="K7">
-        <v>-16</v>
-      </c>
-      <c r="L7">
-        <v>-0.4624277456647399</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>8.01</v>
-      </c>
-      <c r="V7">
-        <v>0.62578125</v>
-      </c>
-      <c r="W7">
-        <v>-0.2061855670103093</v>
-      </c>
-      <c r="X7">
-        <v>0.172096102863786</v>
-      </c>
-      <c r="Y7">
-        <v>-0.3782816698740953</v>
-      </c>
-      <c r="Z7">
-        <v>0.4220850513577476</v>
-      </c>
-      <c r="AA7">
-        <v>-0.2122624246712372</v>
-      </c>
-      <c r="AB7">
-        <v>0.1263766767962246</v>
-      </c>
-      <c r="AC7">
-        <v>-0.3386391014674618</v>
-      </c>
-      <c r="AD7">
-        <v>12</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>12</v>
-      </c>
-      <c r="AG7">
-        <v>3.99</v>
-      </c>
-      <c r="AH7">
-        <v>0.4838709677419354</v>
-      </c>
-      <c r="AI7">
-        <v>0.1181102362204725</v>
-      </c>
-      <c r="AJ7">
-        <v>0.2376414532459798</v>
-      </c>
-      <c r="AK7">
-        <v>0.04263275991024683</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>-0.6976744186046512</v>
-      </c>
-      <c r="AP7">
-        <v>-0.2319767441860465</v>
+        <v>-1.912317327766179</v>
       </c>
     </row>
   </sheetData>
